--- a/Result/profitability/6231.xlsx
+++ b/Result/profitability/6231.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>1.63875</v>
+        <v>1.6375</v>
       </c>
       <c r="N2" t="n">
-        <v>74.86375</v>
+        <v>75.16875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4675</v>
+        <v>1.4575</v>
       </c>
       <c r="N3" t="n">
-        <v>74.6375</v>
+        <v>75.02499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3575</v>
+        <v>1.38625</v>
       </c>
       <c r="N4" t="n">
-        <v>75.28749999999999</v>
+        <v>75.86624999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.32</v>
+        <v>1.43125</v>
       </c>
       <c r="N5" t="n">
-        <v>77.58999999999999</v>
+        <v>78.28999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>1.40625</v>
+        <v>1.41625</v>
       </c>
       <c r="N6" t="n">
-        <v>79.78749999999999</v>
+        <v>80.345</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>1.38625</v>
+        <v>1.37</v>
       </c>
       <c r="N7" t="n">
-        <v>81.22125</v>
+        <v>81.39999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>1.34</v>
+        <v>1.36875</v>
       </c>
       <c r="N8" t="n">
-        <v>82.43625</v>
+        <v>82.61375000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>465</v>
+      </c>
+      <c r="D75" t="n">
+        <v>103</v>
+      </c>
+      <c r="E75" t="n">
+        <v>362</v>
+      </c>
+      <c r="F75" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>110</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>118</v>
+      </c>
+      <c r="K75" t="n">
+        <v>88</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.77875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>74.995</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1352941176470588</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.420000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01857180224954225</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8557692307692306</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.599999999999994</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07747648035417809</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
